--- a/模型价格目录大全.xlsx
+++ b/模型价格目录大全.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>生成 2026-09-24 10:21 ｜ 口径 USD/百万token（$/张、$/秒、$/次、$/小时单标）</t>
+          <t>生成 2026-09-24 17:24 ｜ 口径 USD/百万token（$/张、$/秒、$/次、$/小时单标）</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>枚举</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/模型价格目录大全.xlsx
+++ b/模型价格目录大全.xlsx
@@ -475,14 +475,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>生成 2026-10-19 14:33 ｜ 口径 USD/百万token（$/张、$/秒、$/次、$/小时单标）</t>
+          <t>生成 2026-10-19 18:00 ｜ 口径 USD/百万token（$/张、$/秒、$/次、$/小时单标）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>源新鲜度: bailian_intl_api 2026-10-19 10:20:08 | byteplus 2026-10-19 10:20:46 | aws_bedrock offer 20261012084008 ｜ 抓于 2026-10-14 15:10:01 | azure 2026-10-19 10:20:45 | vertex(GCP) 2026-10-19 10:20:45 | bailian_cn(国内站) 2026-10-19 12:06:09 | model_pages(详情页池) 2026-10-19 10:20</t>
+          <t>源新鲜度: bailian_intl_api 2026-10-19 10:20:08 | byteplus 2026-10-19 10:20:46 | aws_bedrock offer 20261012084008 ｜ 抓于 2026-10-14 15:10:01 | azure 2026-10-19 10:20:45 | vertex(GCP) 2026-10-19 10:20:45 | bailian_cn(国内站) 2026-10-19 17:58:32 | model_pages(详情页池) 2026-10-19 10:20</t>
         </is>
       </c>
     </row>
